--- a/etf_holdings/2026-10-02_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.27%4,200,000</t>
+          <t>13.03%4,200,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.27%</t>
+          <t>13.03%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0%519</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>519</v>
+        <v>5185</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.49%13,000,000</t>
+          <t>8.69%1,350,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.49%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13000000</v>
+        <v>1350000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>+1.35%526</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4975</v>
+        <v>526</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.46%1,350,000</t>
+          <t>8.49%13,000,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.46%</t>
+          <t>8.49%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1350000</v>
+        <v>13000000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+3.4%1215</t>
+          <t>+7.41%1305</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+7.41%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1215</v>
+        <v>1305</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.96%5,200,000</t>
+          <t>8.42%5,200,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.96%</t>
+          <t>8.42%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.82%11835</t>
+          <t>+2.62%12145</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11835</v>
+        <v>12145</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.15%480,000</t>
+          <t>7.24%480,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.15%</t>
+          <t>7.24%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4980</v>
+        <v>4950</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.08%1,130,000</t>
+          <t>6.94%1,130,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.08%</t>
+          <t>6.94%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+5.97%1420</t>
+          <t>+2.82%1460</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1420</v>
+        <v>1460</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6.08%3,400,000</t>
+          <t>6.16%3,400,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.08%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+4.12%1010</t>
+          <t>+3.96%1050</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>+3.96%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1010</v>
+        <v>1050</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.72%4,500,000</t>
+          <t>5.86%4,500,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.72%</t>
+          <t>5.86%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.52%1,250,000</t>
+          <t>5.34%1,250,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>5.34%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+9.85%602</t>
+          <t>+3.99%626</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+3.99%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.55%6,000,000</t>
+          <t>4.66%6,000,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>4.66%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.37%140,500</t>
+          <t>3.29%140,500</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.96%2110</t>
+          <t>-1.18%2085</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2110</v>
+        <v>2085</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.06%1,150,020</t>
+          <t>2.98%1,150,020</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,25 +1236,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+7.71%852</t>
+          <t>-1.3%2660</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+7.71%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>852</v>
+        <v>2660</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.90%2,700,000</t>
+          <t>2.90%800,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1263,11 +1263,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>2700000</v>
+        <v>800000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.3%2660</t>
+          <t>-2%835</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2660</v>
+        <v>835</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.68%800,000</t>
+          <t>2.80%2,700,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>800000</v>
+        <v>2700000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:32</t>
+          <t>2026-10-02 19:05:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.59%254</t>
+          <t>+2.36%260</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.56%8,000,000</t>
+          <t>2.58%8,000,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.1%6875</t>
+          <t>-1.09%6800</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6875</v>
+        <v>6800</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.51%290,000</t>
+          <t>2.45%290,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+4.53%161.5</t>
+          <t>0%161.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.12%10,400,000</t>
+          <t>2.08%10,400,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.79%1905</t>
+          <t>-1.05%1885</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.09%871,000</t>
+          <t>2.04%871,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,33 +1607,33 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1%710</t>
+          <t>+0.42%713</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.81%2,030,000</t>
+          <t>1.50%1,700,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2030000</v>
+        <v>1700000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-3.19%94.2</t>
+          <t>+6.16%100</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>+6.16%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.01%8,500,000</t>
+          <t>1.05%8,500,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+7.04%1900</t>
+          <t>+3.42%1965</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+7.04%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1900</v>
+        <v>1965</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.48%200,000</t>
+          <t>0.49%200,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+4.37%6205</t>
+          <t>+1.37%6290</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6205</v>
+        <v>6290</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.27%5490</t>
+          <t>+1.64%5580</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5490</v>
+        <v>5580</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.15%334</t>
+          <t>-0.6%332</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.54%2555</t>
+          <t>-0.59%2540</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2555</v>
+        <v>2540</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.99%254</t>
+          <t>-1.18%251</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.58%2080</t>
+          <t>+5.29%2190</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2080</v>
+        <v>2190</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.63%238</t>
+          <t>+0.84%240</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:33</t>
+          <t>2026-10-02 19:05:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+3.25%190.5</t>
+          <t>+0.99%1535</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+3.25%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>190.5</v>
+        <v>1535</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,21 +2395,21 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.93%184.5</t>
+          <t>-2.1%186.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>184.5</v>
+        <v>186.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.99%1535</t>
+          <t>+1.93%184.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1535</v>
+        <v>184.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.33%150.5</t>
+          <t>0%150.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.45%110.5</t>
+          <t>+0.9%111.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>110.5</v>
+        <v>111.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.42%965</t>
+          <t>-0.31%962</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.26%762</t>
+          <t>-1.05%754</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,25 +2761,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2891中信金</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.73%67.9</t>
+          <t>-0.89%66.8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>67.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%9,360</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>9000</v>
+        <v>9360</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>2891中信金</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.61%67.4</t>
+          <t>-0.88%67.3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>67.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,360</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>9360</v>
+        <v>9000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.76%529</t>
+          <t>+2.46%542</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2884玉山金</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.11%45.35</t>
+          <t>-0.17%295.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>45.35</v>
+        <v>295.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,450</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>9000</v>
+        <v>1450</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,21 +3005,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2886兆豐金</t>
+          <t>2884玉山金</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.61%48.85</t>
+          <t>0%45.35</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>48.85</v>
+        <v>45.35</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2880華南金</t>
+          <t>2886兆豐金</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.22%45.25</t>
+          <t>0%48.85</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>45.25</v>
+        <v>48.85</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,090</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2880華南金</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.51%296</t>
+          <t>-0.88%44.85</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>296</v>
+        <v>44.85</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,450</t>
+          <t>&lt;0.01%9,090</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1450</v>
+        <v>9090</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:35</t>
+          <t>2026-10-02 19:05:09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,21 +3188,21 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2887台新新光金</t>
+          <t>2883凱基金</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.67%41.25</t>
+          <t>+1.22%37.35</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>+1.22%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>41.25</v>
+        <v>37.35</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:36</t>
+          <t>2026-10-02 19:05:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,21 +3249,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2890永豐金</t>
+          <t>2887台新新光金</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.36%43.65</t>
+          <t>-1.7%40.55</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>43.65</v>
+        <v>40.55</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:36</t>
+          <t>2026-10-02 19:05:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,21 +3310,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2883凱基金</t>
+          <t>2890永豐金</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-5.02%36.9</t>
+          <t>+0.92%44.05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-5.02%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>36.9</v>
+        <v>44.05</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:36</t>
+          <t>2026-10-02 19:05:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.88%224.5</t>
+          <t>+0.67%226</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>224.5</v>
+        <v>226</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:36</t>
+          <t>2026-10-02 19:05:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+3.41%212.5</t>
+          <t>+0.47%213.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+3.41%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>212.5</v>
+        <v>213.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:36</t>
+          <t>2026-10-02 19:05:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.39%145.5</t>
+          <t>+0.34%146</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>145.5</v>
+        <v>146</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-02_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:07</t>
+          <t>2026-10-02 22:49:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:08</t>
+          <t>2026-10-02 22:49:13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:09</t>
+          <t>2026-10-02 22:49:25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:11</t>
+          <t>2026-10-02 22:49:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:11</t>
+          <t>2026-10-02 22:49:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:11</t>
+          <t>2026-10-02 22:49:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:11</t>
+          <t>2026-10-02 22:49:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:11</t>
+          <t>2026-10-02 22:49:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:02</t>
+          <t>2026-10-02 22:58:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:13</t>
+          <t>2026-10-02 22:58:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:25</t>
+          <t>2026-10-02 22:58:13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:36</t>
+          <t>2026-10-02 22:58:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:36</t>
+          <t>2026-10-02 22:58:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:36</t>
+          <t>2026-10-02 22:58:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:36</t>
+          <t>2026-10-02 22:58:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:36</t>
+          <t>2026-10-02 22:58:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:10</t>
+          <t>2026-10-02 23:48:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:12</t>
+          <t>2026-10-02 23:48:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:13</t>
+          <t>2026-10-02 23:48:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:14</t>
+          <t>2026-10-02 23:48:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:14</t>
+          <t>2026-10-02 23:48:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:14</t>
+          <t>2026-10-02 23:48:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:14</t>
+          <t>2026-10-02 23:48:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:14</t>
+          <t>2026-10-02 23:48:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
